--- a/bench/results/3090/matmul.xlsx
+++ b/bench/results/3090/matmul.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G351"/>
+  <dimension ref="A1:G401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.025843</t>
+          <t>0.027462</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -497,7 +497,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.025834</t>
+          <t>0.027678</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -524,7 +524,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.025610</t>
+          <t>0.027210</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,7 +551,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.027919</t>
+          <t>0.029129</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -578,7 +578,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.026553</t>
+          <t>0.028743</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -605,7 +605,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.025460</t>
+          <t>0.027353</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.025853</t>
+          <t>0.027978</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.025453</t>
+          <t>0.030619</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.030349</t>
+          <t>0.030616</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.048831</t>
+          <t>0.048102</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.027100</t>
+          <t>0.027038</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -767,7 +767,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.025215</t>
+          <t>0.033647</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -794,7 +794,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.031698</t>
+          <t>0.032148</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -821,7 +821,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.038490</t>
+          <t>0.038864</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -848,7 +848,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.057720</t>
+          <t>0.057237</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.028853</t>
+          <t>0.030315</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -902,7 +902,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.031230</t>
+          <t>0.031166</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.040914</t>
+          <t>0.041339</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -956,7 +956,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.057905</t>
+          <t>0.057610</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.095206</t>
+          <t>0.094931</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.029631</t>
+          <t>0.030663</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.041050</t>
+          <t>0.040949</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.060786</t>
+          <t>0.060346</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.096980</t>
+          <t>0.096807</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.171415</t>
+          <t>0.170571</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.027564</t>
+          <t>0.028082</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.027973</t>
+          <t>0.028364</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.027457</t>
+          <t>0.028395</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.033317</t>
+          <t>0.034966</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.029816</t>
+          <t>0.030728</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.027039</t>
+          <t>0.028724</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.031266</t>
+          <t>0.032683</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.026942</t>
+          <t>0.028225</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.028720</t>
+          <t>0.028938</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.039361</t>
+          <t>0.039417</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.031243</t>
+          <t>0.032213</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.031407</t>
+          <t>0.033055</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.035589</t>
+          <t>0.036103</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.037433</t>
+          <t>0.038559</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.058130</t>
+          <t>0.058039</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.029786</t>
+          <t>0.031375</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.036462</t>
+          <t>0.036627</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.052376</t>
+          <t>0.051991</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.057830</t>
+          <t>0.058448</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.111356</t>
+          <t>0.109804</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.033137</t>
+          <t>0.033055</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.049847</t>
+          <t>0.049255</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.070874</t>
+          <t>0.069593</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.097050</t>
+          <t>0.100965</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.196007</t>
+          <t>0.193916</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.027489</t>
+          <t>0.028357</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.031366</t>
+          <t>0.032526</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.027413</t>
+          <t>0.028313</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.033213</t>
+          <t>0.034628</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.030211</t>
+          <t>0.030451</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.031287</t>
+          <t>0.033443</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.031525</t>
+          <t>0.032710</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.026710</t>
+          <t>0.028052</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.029149</t>
+          <t>0.028965</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.039527</t>
+          <t>0.039489</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.031564</t>
+          <t>0.032633</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.031167</t>
+          <t>0.032469</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.035762</t>
+          <t>0.035202</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.037542</t>
+          <t>0.037631</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.058383</t>
+          <t>0.058304</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.029579</t>
+          <t>0.031941</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.038467</t>
+          <t>0.037256</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.052818</t>
+          <t>0.052484</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.057621</t>
+          <t>0.058216</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.112049</t>
+          <t>0.111023</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.032938</t>
+          <t>0.033754</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0.051543</t>
+          <t>0.050072</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.071209</t>
+          <t>0.070525</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0.097697</t>
+          <t>0.098119</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0.196524</t>
+          <t>0.194651</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.031524</t>
+          <t>0.033521</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0.031369</t>
+          <t>0.032586</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0.027254</t>
+          <t>0.029197</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0.033370</t>
+          <t>0.035644</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.030584</t>
+          <t>0.030341</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.031507</t>
+          <t>0.032889</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0.031653</t>
+          <t>0.037811</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0.026506</t>
+          <t>0.035668</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0.034542</t>
+          <t>0.041646</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0.040111</t>
+          <t>0.041510</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0.033502</t>
+          <t>0.032717</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0.031521</t>
+          <t>0.032634</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.035426</t>
+          <t>0.035359</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0.038015</t>
+          <t>0.037312</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0.058948</t>
+          <t>0.057954</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.029922</t>
+          <t>0.031319</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0.037341</t>
+          <t>0.036482</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0.052701</t>
+          <t>0.052173</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0.058052</t>
+          <t>0.057916</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0.111993</t>
+          <t>0.110429</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0.033337</t>
+          <t>0.033050</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0.050774</t>
+          <t>0.050138</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0.071294</t>
+          <t>0.069850</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0.101180</t>
+          <t>0.098819</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0.199077</t>
+          <t>0.195924</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0.031662</t>
+          <t>0.033901</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0.031200</t>
+          <t>0.033572</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0.027438</t>
+          <t>0.029750</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.033580</t>
+          <t>0.035932</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.031369</t>
+          <t>0.031288</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.031563</t>
+          <t>0.033061</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.031552</t>
+          <t>0.032757</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.026396</t>
+          <t>0.028112</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.034662</t>
+          <t>0.036230</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0.039884</t>
+          <t>0.039841</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0.031957</t>
+          <t>0.032772</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0.031174</t>
+          <t>0.032694</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0.035777</t>
+          <t>0.036019</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0.037755</t>
+          <t>0.038716</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0.058794</t>
+          <t>0.058914</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0.029790</t>
+          <t>0.032383</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0.037525</t>
+          <t>0.037826</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0.053232</t>
+          <t>0.052687</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0.058569</t>
+          <t>0.058741</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0.096270</t>
+          <t>0.097074</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>0.033170</t>
+          <t>0.033411</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>0.050969</t>
+          <t>0.050998</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>0.070392</t>
+          <t>0.070351</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>0.098757</t>
+          <t>0.098946</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>0.197903</t>
+          <t>0.196343</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>0.033776</t>
+          <t>0.035426</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.033405</t>
+          <t>0.034496</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.033291</t>
+          <t>0.034646</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.026424</t>
+          <t>0.027475</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.029335</t>
+          <t>0.029315</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.033554</t>
+          <t>0.034877</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.033094</t>
+          <t>0.034516</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.026777</t>
+          <t>0.028018</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.028895</t>
+          <t>0.029469</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>0.038726</t>
+          <t>0.038802</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>0.031654</t>
+          <t>0.032168</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0.033246</t>
+          <t>0.035052</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0.035357</t>
+          <t>0.036828</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0.039123</t>
+          <t>0.039656</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>0.057850</t>
+          <t>0.057919</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>0.031552</t>
+          <t>0.032621</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>0.035006</t>
+          <t>0.035962</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>0.044617</t>
+          <t>0.042560</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>0.058781</t>
+          <t>0.059090</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>0.095851</t>
+          <t>0.095995</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0.033208</t>
+          <t>0.033179</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.042995</t>
+          <t>0.042241</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.062372</t>
+          <t>0.062529</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.097209</t>
+          <t>0.097357</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.174318</t>
+          <t>0.174048</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.033525</t>
+          <t>0.035097</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.027345</t>
+          <t>0.028622</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.026056</t>
+          <t>0.029048</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>0.026442</t>
+          <t>0.027880</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>0.030393</t>
+          <t>0.030445</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>0.029016</t>
+          <t>0.030695</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>0.033299</t>
+          <t>0.034814</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>0.032994</t>
+          <t>0.033894</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>0.028873</t>
+          <t>0.029438</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>0.041877</t>
+          <t>0.040646</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>0.031752</t>
+          <t>0.032804</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>0.033896</t>
+          <t>0.034973</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>0.034476</t>
+          <t>0.034507</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>0.038856</t>
+          <t>0.040377</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>0.060081</t>
+          <t>0.060476</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>0.031386</t>
+          <t>0.043067</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>0.032203</t>
+          <t>0.032095</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>0.047147</t>
+          <t>0.044574</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.062427</t>
+          <t>0.061262</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.099372</t>
+          <t>0.098178</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.034377</t>
+          <t>0.033364</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.044117</t>
+          <t>0.049141</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.064919</t>
+          <t>0.066601</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.101617</t>
+          <t>0.103019</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.266764</t>
+          <t>0.267910</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>0.033615</t>
+          <t>0.034988</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.026733</t>
+          <t>0.027927</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.026149</t>
+          <t>0.028212</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.026180</t>
+          <t>0.027660</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>0.038186</t>
+          <t>0.038477</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.033283</t>
+          <t>0.034839</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.028023</t>
+          <t>0.029478</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.026261</t>
+          <t>0.028392</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.035381</t>
+          <t>0.036103</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.055682</t>
+          <t>0.055435</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.033477</t>
+          <t>0.035380</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.030923</t>
+          <t>0.030465</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.036187</t>
+          <t>0.036039</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.053223</t>
+          <t>0.053284</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>0.090780</t>
+          <t>0.090410</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>0.030782</t>
+          <t>0.031786</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>0.049195</t>
+          <t>0.048918</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>0.054178</t>
+          <t>0.055286</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>0.089743</t>
+          <t>0.089838</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>0.163596</t>
+          <t>0.164021</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>0.040029</t>
+          <t>0.044242</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>0.072049</t>
+          <t>0.074338</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>0.092856</t>
+          <t>0.094554</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.165836</t>
+          <t>0.166955</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.312735</t>
+          <t>0.309043</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.027845</t>
+          <t>0.033647</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.025337</t>
+          <t>0.029650</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.027239</t>
+          <t>0.029363</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.036625</t>
+          <t>0.037095</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>0.058298</t>
+          <t>0.055465</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>0.028079</t>
+          <t>0.030291</t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>0.026904</t>
+          <t>0.028779</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>0.037449</t>
+          <t>0.037790</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>0.059724</t>
+          <t>0.059705</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>0.090007</t>
+          <t>0.089506</t>
         </is>
       </c>
       <c r="F211" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>0.032949</t>
+          <t>0.033058</t>
         </is>
       </c>
       <c r="F212" t="n">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>0.036339</t>
+          <t>0.036366</t>
         </is>
       </c>
       <c r="F213" t="n">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>0.052849</t>
+          <t>0.053105</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>0.088184</t>
+          <t>0.087162</t>
         </is>
       </c>
       <c r="F215" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>0.159053</t>
+          <t>0.160008</t>
         </is>
       </c>
       <c r="F216" t="n">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>0.043391</t>
+          <t>0.043273</t>
         </is>
       </c>
       <c r="F217" t="n">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>0.052426</t>
+          <t>0.052497</t>
         </is>
       </c>
       <c r="F218" t="n">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>0.089544</t>
+          <t>0.088352</t>
         </is>
       </c>
       <c r="F219" t="n">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>0.150807</t>
+          <t>0.150479</t>
         </is>
       </c>
       <c r="F220" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>0.299385</t>
+          <t>0.298324</t>
         </is>
       </c>
       <c r="F221" t="n">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>0.062351</t>
+          <t>0.060875</t>
         </is>
       </c>
       <c r="F222" t="n">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>0.081978</t>
+          <t>0.080976</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>0.161829</t>
+          <t>0.160402</t>
         </is>
       </c>
       <c r="F224" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>0.296246</t>
+          <t>0.291677</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>0.583943</t>
+          <t>0.577808</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>0.027468</t>
+          <t>0.029210</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>0.027289</t>
+          <t>0.027961</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>0.053449</t>
+          <t>0.053377</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>0.056473</t>
+          <t>0.055994</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>0.102446</t>
+          <t>0.101187</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>0.030447</t>
+          <t>0.029597</t>
         </is>
       </c>
       <c r="F232" t="n">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>0.035731</t>
+          <t>0.035908</t>
         </is>
       </c>
       <c r="F233" t="n">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>0.079544</t>
+          <t>0.080294</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>0.090532</t>
+          <t>0.089656</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>0.165996</t>
+          <t>0.163537</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>0.036948</t>
+          <t>0.036890</t>
         </is>
       </c>
       <c r="F237" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>0.053493</t>
+          <t>0.053033</t>
         </is>
       </c>
       <c r="F238" t="n">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>0.131629</t>
+          <t>0.130810</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>0.162164</t>
+          <t>0.156609</t>
         </is>
       </c>
       <c r="F240" t="n">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>0.307283</t>
+          <t>0.304097</t>
         </is>
       </c>
       <c r="F241" t="n">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>0.054876</t>
+          <t>0.054523</t>
         </is>
       </c>
       <c r="F242" t="n">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>0.094336</t>
+          <t>0.092790</t>
         </is>
       </c>
       <c r="F243" t="n">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>0.178157</t>
+          <t>0.175082</t>
         </is>
       </c>
       <c r="F244" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>0.302715</t>
+          <t>0.293972</t>
         </is>
       </c>
       <c r="F245" t="n">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>0.537445</t>
+          <t>0.532323</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>0.094039</t>
+          <t>0.093300</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>0.162456</t>
+          <t>0.159783</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>0.322983</t>
+          <t>0.317390</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.580604</t>
+          <t>0.573523</t>
         </is>
       </c>
       <c r="F250" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>1.488556</t>
+          <t>1.473522</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>0.026619</t>
+          <t>0.026855</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0.037667</t>
+          <t>0.036171</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>0.055214</t>
+          <t>0.053775</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.099516</t>
+          <t>0.095759</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>0.185980</t>
+          <t>0.182554</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>0.035857</t>
+          <t>0.034912</t>
         </is>
       </c>
       <c r="F257" t="n">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>0.055308</t>
+          <t>0.055330</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>0.090363</t>
+          <t>0.088368</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>0.167655</t>
+          <t>0.163043</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>0.323700</t>
+          <t>0.317539</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0.054587</t>
+          <t>0.052972</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>0.090103</t>
+          <t>0.087005</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>0.161665</t>
+          <t>0.157263</t>
         </is>
       </c>
       <c r="F264" t="n">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>0.315424</t>
+          <t>0.310512</t>
         </is>
       </c>
       <c r="F265" t="n">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>0.605885</t>
+          <t>0.598123</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>0.090616</t>
+          <t>0.089019</t>
         </is>
       </c>
       <c r="F267" t="n">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>0.161705</t>
+          <t>0.159101</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.301810</t>
+          <t>0.293924</t>
         </is>
       </c>
       <c r="F269" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.558792</t>
+          <t>0.553971</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>1.171113</t>
+          <t>1.154944</t>
         </is>
       </c>
       <c r="F271" t="n">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.167432</t>
+          <t>0.164172</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>0.302774</t>
+          <t>0.296800</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>0.583645</t>
+          <t>0.572635</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>1.099556</t>
+          <t>1.083068</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2.305482</t>
+          <t>2.276450</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>0.038750</t>
+          <t>0.036771</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>0.055299</t>
+          <t>0.053872</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>0.093069</t>
+          <t>0.090907</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>0.177184</t>
+          <t>0.173891</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>0.314867</t>
+          <t>0.309997</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>0.056246</t>
+          <t>0.054343</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>0.090023</t>
+          <t>0.087916</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>0.168239</t>
+          <t>0.164740</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>0.290659</t>
+          <t>0.283281</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>0.534754</t>
+          <t>0.523745</t>
         </is>
       </c>
       <c r="F286" t="n">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>0.092280</t>
+          <t>0.090210</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>0.163410</t>
+          <t>0.157323</t>
         </is>
       </c>
       <c r="F288" t="n">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>0.294568</t>
+          <t>0.289111</t>
         </is>
       </c>
       <c r="F289" t="n">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>0.562907</t>
+          <t>0.550342</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>1.071183</t>
+          <t>1.049325</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>0.163372</t>
+          <t>0.161672</t>
         </is>
       </c>
       <c r="F292" t="n">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>0.304081</t>
+          <t>0.298017</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>0.565753</t>
+          <t>0.554230</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>1.117925</t>
+          <t>1.093862</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2.051110</t>
+          <t>2.012187</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>0.333657</t>
+          <t>0.325699</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>0.593172</t>
+          <t>0.575500</t>
         </is>
       </c>
       <c r="F298" t="n">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>1.054353</t>
+          <t>1.030789</t>
         </is>
       </c>
       <c r="F299" t="n">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2.223034</t>
+          <t>2.175695</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>4.218205</t>
+          <t>4.109917</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>0.057392</t>
+          <t>0.055905</t>
         </is>
       </c>
       <c r="F302" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>0.105556</t>
+          <t>0.102582</t>
         </is>
       </c>
       <c r="F303" t="n">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>0.158616</t>
+          <t>0.153144</t>
         </is>
       </c>
       <c r="F304" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>0.305293</t>
+          <t>0.300919</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>0.573748</t>
+          <t>0.559929</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>0.093833</t>
+          <t>0.089614</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>0.176249</t>
+          <t>0.171520</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>0.293611</t>
+          <t>0.284496</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>0.541716</t>
+          <t>0.526805</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1.036045</t>
+          <t>1.012209</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>0.168706</t>
+          <t>0.163800</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>0.319106</t>
+          <t>0.311595</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>0.564164</t>
+          <t>0.549077</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1.084184</t>
+          <t>1.052848</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.024127</t>
+          <t>1.967519</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>0.313905</t>
+          <t>0.304187</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>0.611459</t>
+          <t>0.594606</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>1.120129</t>
+          <t>1.087019</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2.117603</t>
+          <t>2.056863</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>3.971060</t>
+          <t>3.847488</t>
         </is>
       </c>
       <c r="F321" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>0.612403</t>
+          <t>0.592376</t>
         </is>
       </c>
       <c r="F322" t="n">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>1.204568</t>
+          <t>1.161044</t>
         </is>
       </c>
       <c r="F323" t="n">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2.116327</t>
+          <t>2.046324</t>
         </is>
       </c>
       <c r="F324" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>4.262310</t>
+          <t>4.123031</t>
         </is>
       </c>
       <c r="F325" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>8.266278</t>
+          <t>8.004435</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.097285</t>
+          <t>0.095403</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.158564</t>
+          <t>0.153751</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.314740</t>
+          <t>0.308286</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.578933</t>
+          <t>0.561231</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>1.106493</t>
+          <t>1.069865</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.173674</t>
+          <t>0.168601</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.295993</t>
+          <t>0.284796</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.572215</t>
+          <t>0.553574</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>1.048458</t>
+          <t>1.013797</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2.082678</t>
+          <t>2.011382</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>0.298550</t>
+          <t>0.287691</t>
         </is>
       </c>
       <c r="F337" t="n">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>0.555071</t>
+          <t>0.535275</t>
         </is>
       </c>
       <c r="F338" t="n">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>1.108795</t>
+          <t>1.057777</t>
         </is>
       </c>
       <c r="F339" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2.085406</t>
+          <t>2.006082</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>3.956419</t>
+          <t>3.809966</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>0.565436</t>
+          <t>0.544279</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>1.069149</t>
+          <t>1.027347</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2.076998</t>
+          <t>2.001238</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>4.170632</t>
+          <t>4.016517</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>7.774656</t>
+          <t>7.485758</t>
         </is>
       </c>
       <c r="F346" t="n">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>1.098507</t>
+          <t>1.058301</t>
         </is>
       </c>
       <c r="F347" t="n">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2.088334</t>
+          <t>2.007662</t>
         </is>
       </c>
       <c r="F348" t="n">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>4.046326</t>
+          <t>3.887964</t>
         </is>
       </c>
       <c r="F349" t="n">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>8.333249</t>
+          <t>8.014836</t>
         </is>
       </c>
       <c r="F350" t="n">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>16.608701</t>
+          <t>16.019122</t>
         </is>
       </c>
       <c r="F351" t="n">
@@ -9901,6 +9901,1356 @@
       </c>
       <c r="G351" t="n">
         <v>402653184</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C352" t="n">
+        <v>512</v>
+      </c>
+      <c r="D352" t="n">
+        <v>512</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>0.156466</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>8589934592</v>
+      </c>
+      <c r="G352" t="n">
+        <v>34078720</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C353" t="n">
+        <v>512</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>0.275963</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>17179869184</v>
+      </c>
+      <c r="G353" t="n">
+        <v>51380224</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C354" t="n">
+        <v>512</v>
+      </c>
+      <c r="D354" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>0.562909</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>34359738368</v>
+      </c>
+      <c r="G354" t="n">
+        <v>85983232</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C355" t="n">
+        <v>512</v>
+      </c>
+      <c r="D355" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>1.067264</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>68719476736</v>
+      </c>
+      <c r="G355" t="n">
+        <v>155189248</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C356" t="n">
+        <v>512</v>
+      </c>
+      <c r="D356" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2.106281</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>137438953472</v>
+      </c>
+      <c r="G356" t="n">
+        <v>293601280</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C357" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D357" t="n">
+        <v>512</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>0.286679</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>17179869184</v>
+      </c>
+      <c r="G357" t="n">
+        <v>51380224</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C358" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D358" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>0.542841</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>34359738368</v>
+      </c>
+      <c r="G358" t="n">
+        <v>69206016</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C359" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D359" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>1.024968</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>68719476736</v>
+      </c>
+      <c r="G359" t="n">
+        <v>104857600</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C360" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D360" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>2.038390</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>137438953472</v>
+      </c>
+      <c r="G360" t="n">
+        <v>176160768</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C361" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D361" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>3.934374</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>274877906944</v>
+      </c>
+      <c r="G361" t="n">
+        <v>318767104</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C362" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D362" t="n">
+        <v>512</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>0.538702</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>34359738368</v>
+      </c>
+      <c r="G362" t="n">
+        <v>85983232</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C363" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D363" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>1.014502</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>68719476736</v>
+      </c>
+      <c r="G363" t="n">
+        <v>104857600</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C364" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D364" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>2.038054</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>137438953472</v>
+      </c>
+      <c r="G364" t="n">
+        <v>142606336</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C365" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D365" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>3.803688</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>274877906944</v>
+      </c>
+      <c r="G365" t="n">
+        <v>218103808</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C366" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D366" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>7.593960</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>549755813888</v>
+      </c>
+      <c r="G366" t="n">
+        <v>369098752</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C367" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D367" t="n">
+        <v>512</v>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>1.043133</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>68719476736</v>
+      </c>
+      <c r="G367" t="n">
+        <v>155189248</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C368" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D368" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>2.034688</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>137438953472</v>
+      </c>
+      <c r="G368" t="n">
+        <v>176160768</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C369" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D369" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>3.864329</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>274877906944</v>
+      </c>
+      <c r="G369" t="n">
+        <v>218103808</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C370" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D370" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>7.453279</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>549755813888</v>
+      </c>
+      <c r="G370" t="n">
+        <v>301989888</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C371" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D371" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>14.943165</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>1099511627776</v>
+      </c>
+      <c r="G371" t="n">
+        <v>469762048</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C372" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D372" t="n">
+        <v>512</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>2.027448</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>137438953472</v>
+      </c>
+      <c r="G372" t="n">
+        <v>293601280</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C373" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D373" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>3.906169</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>274877906944</v>
+      </c>
+      <c r="G373" t="n">
+        <v>318767104</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C374" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D374" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>7.529883</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>549755813888</v>
+      </c>
+      <c r="G374" t="n">
+        <v>369098752</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C375" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D375" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>14.813606</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>1099511627776</v>
+      </c>
+      <c r="G375" t="n">
+        <v>469762048</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C376" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D376" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>29.598545</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>2199023255552</v>
+      </c>
+      <c r="G376" t="n">
+        <v>671088640</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C377" t="n">
+        <v>512</v>
+      </c>
+      <c r="D377" t="n">
+        <v>512</v>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>0.283187</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>17179869184</v>
+      </c>
+      <c r="G377" t="n">
+        <v>67633152</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C378" t="n">
+        <v>512</v>
+      </c>
+      <c r="D378" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>0.555747</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>34359738368</v>
+      </c>
+      <c r="G378" t="n">
+        <v>101711872</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C379" t="n">
+        <v>512</v>
+      </c>
+      <c r="D379" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>1.071825</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>68719476736</v>
+      </c>
+      <c r="G379" t="n">
+        <v>169869312</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C380" t="n">
+        <v>512</v>
+      </c>
+      <c r="D380" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>2.104754</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>137438953472</v>
+      </c>
+      <c r="G380" t="n">
+        <v>306184192</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C381" t="n">
+        <v>512</v>
+      </c>
+      <c r="D381" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>4.183628</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>274877906944</v>
+      </c>
+      <c r="G381" t="n">
+        <v>578813952</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C382" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D382" t="n">
+        <v>512</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>0.530998</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>34359738368</v>
+      </c>
+      <c r="G382" t="n">
+        <v>101711872</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C383" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D383" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>1.022507</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>68719476736</v>
+      </c>
+      <c r="G383" t="n">
+        <v>136314880</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C384" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D384" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>1.972652</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>137438953472</v>
+      </c>
+      <c r="G384" t="n">
+        <v>205520896</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C385" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D385" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>4.067001</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>274877906944</v>
+      </c>
+      <c r="G385" t="n">
+        <v>343932928</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C386" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D386" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>7.843290</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>549755813888</v>
+      </c>
+      <c r="G386" t="n">
+        <v>620756992</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C387" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D387" t="n">
+        <v>512</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>1.067012</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>68719476736</v>
+      </c>
+      <c r="G387" t="n">
+        <v>169869312</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C388" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D388" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>1.956523</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>137438953472</v>
+      </c>
+      <c r="G388" t="n">
+        <v>205520896</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C389" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D389" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>3.802301</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>274877906944</v>
+      </c>
+      <c r="G389" t="n">
+        <v>276824064</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C390" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D390" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>7.611462</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>549755813888</v>
+      </c>
+      <c r="G390" t="n">
+        <v>419430400</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C391" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D391" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>15.184390</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>1099511627776</v>
+      </c>
+      <c r="G391" t="n">
+        <v>704643072</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C392" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D392" t="n">
+        <v>512</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>2.018759</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>137438953472</v>
+      </c>
+      <c r="G392" t="n">
+        <v>306184192</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C393" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D393" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>3.827181</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>274877906944</v>
+      </c>
+      <c r="G393" t="n">
+        <v>343932928</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C394" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D394" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>7.456802</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>549755813888</v>
+      </c>
+      <c r="G394" t="n">
+        <v>419430400</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C395" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D395" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>14.973366</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>1099511627776</v>
+      </c>
+      <c r="G395" t="n">
+        <v>570425344</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C396" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D396" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>29.857834</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>2199023255552</v>
+      </c>
+      <c r="G396" t="n">
+        <v>872415232</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C397" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D397" t="n">
+        <v>512</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>3.924019</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>274877906944</v>
+      </c>
+      <c r="G397" t="n">
+        <v>578813952</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C398" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D398" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>7.555870</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>549755813888</v>
+      </c>
+      <c r="G398" t="n">
+        <v>620756992</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C399" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D399" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>14.767519</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>1099511627776</v>
+      </c>
+      <c r="G399" t="n">
+        <v>704643072</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C400" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D400" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>29.618658</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>2199023255552</v>
+      </c>
+      <c r="G400" t="n">
+        <v>872415232</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>matmul</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>32768</v>
+      </c>
+      <c r="C401" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D401" t="n">
+        <v>8192</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>59.249989</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>4398046511104</v>
+      </c>
+      <c r="G401" t="n">
+        <v>1207959552</v>
       </c>
     </row>
   </sheetData>
